--- a/data/trans_bre/IP08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 2,81</t>
+          <t>-9,97; 3,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 4,96</t>
+          <t>-9,77; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,59</t>
+          <t>-8,7; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 6,11</t>
+          <t>-15,58; 5,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 33,93</t>
+          <t>-60,6; 36,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 39,8</t>
+          <t>-47,18; 32,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 37,47</t>
+          <t>-64,26; 45,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 48,55</t>
+          <t>-65,27; 42,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,55</t>
+          <t>-9,04; 0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,45</t>
+          <t>-6,89; 2,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,66</t>
+          <t>-3,48; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -1,37</t>
+          <t>-12,01; -2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 6,13</t>
+          <t>-52,83; 4,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 19,19</t>
+          <t>-42,38; 24,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 72,7</t>
+          <t>-35,27; 79,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,89; -13,95</t>
+          <t>-75,1; -18,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 5,83</t>
+          <t>-6,21; 6,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 8,96</t>
+          <t>-2,55; 9,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,87</t>
+          <t>-1,49; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 4,42</t>
+          <t>-7,74; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 77,63</t>
+          <t>-46,43; 82,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 129,75</t>
+          <t>-21,23; 135,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 306,26</t>
+          <t>-39,87; 293,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 57,6</t>
+          <t>-53,53; 45,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,31</t>
+          <t>-8,43; -0,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -0,51</t>
+          <t>-10,6; -0,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,8</t>
+          <t>-5,17; 3,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 3,91</t>
+          <t>-13,21; 4,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 1,6</t>
+          <t>-76,58; -7,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,29; -1,98</t>
+          <t>-66,58; -3,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 82,45</t>
+          <t>-60,57; 82,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 42,59</t>
+          <t>-66,27; 44,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,73</t>
+          <t>-5,85; -0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,8</t>
+          <t>-4,6; 1,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,95</t>
+          <t>-2,51; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,02</t>
+          <t>-8,46; -0,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,33; -6,67</t>
+          <t>-45,83; -4,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 7,29</t>
+          <t>-30,91; 8,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 33,25</t>
+          <t>-31,72; 34,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 2,13</t>
+          <t>-50,79; 1,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 3,29</t>
+          <t>-9,53; 3,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 4,32</t>
+          <t>-9,25; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 2,62</t>
+          <t>-8,88; 2,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 5,58</t>
+          <t>-15,13; 5,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 36,8</t>
+          <t>-60,13; 35,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 32,91</t>
+          <t>-45,48; 33,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 45,32</t>
+          <t>-64,82; 42,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 42,1</t>
+          <t>-62,43; 47,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,28</t>
+          <t>-8,63; 1,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 2,72</t>
+          <t>-7,38; 2,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,71</t>
+          <t>-3,93; 4,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -2,27</t>
+          <t>-11,52; -1,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 4,55</t>
+          <t>-52,8; 14,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 24,01</t>
+          <t>-43,88; 23,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 79,96</t>
+          <t>-38,37; 74,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -18,49</t>
+          <t>-73,62; -9,86</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 6,13</t>
+          <t>-6,0; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 9,23</t>
+          <t>-2,18; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,93</t>
+          <t>-1,81; 4,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 3,77</t>
+          <t>-6,62; 4,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 82,22</t>
+          <t>-46,24; 72,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 135,29</t>
+          <t>-20,78; 144,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 293,26</t>
+          <t>-45,16; 283,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 45,9</t>
+          <t>-49,03; 63,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -0,75</t>
+          <t>-8,26; -0,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -0,38</t>
+          <t>-10,41; 0,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,56</t>
+          <t>-5,09; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 4,09</t>
+          <t>-13,64; 4,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,58; -7,57</t>
+          <t>-77,5; -10,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -3,25</t>
+          <t>-66,08; 3,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 82,14</t>
+          <t>-56,3; 99,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 44,69</t>
+          <t>-64,56; 44,54</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,44</t>
+          <t>-5,86; -0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,04</t>
+          <t>-4,73; 0,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,99</t>
+          <t>-2,53; 2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; -0,05</t>
+          <t>-7,98; 0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -4,44</t>
+          <t>-45,94; -3,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 8,28</t>
+          <t>-32,0; 6,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 34,75</t>
+          <t>-32,16; 34,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 1,26</t>
+          <t>-50,96; 1,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-3,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,74%</t>
+          <t>-19,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 3,37</t>
+          <t>-9,7; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 4,36</t>
+          <t>-9,29; 4,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 2,67</t>
+          <t>-8,51; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 5,71</t>
+          <t>-15,1; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 35,39</t>
+          <t>-62,58; 33,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 33,66</t>
+          <t>-45,4; 39,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 42,55</t>
+          <t>-66,3; 37,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,43; 47,42</t>
+          <t>-61,42; 55,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,58</t>
+          <t>-5,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-53,01%</t>
+          <t>-49,09%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 1,17</t>
+          <t>-8,48; 0,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 2,67</t>
+          <t>-7,17; 2,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,52</t>
+          <t>-3,77; 4,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -1,85</t>
+          <t>-10,59; -0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 14,36</t>
+          <t>-52,82; 6,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 23,52</t>
+          <t>-42,72; 19,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 74,08</t>
+          <t>-37,53; 72,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,62; -9,86</t>
+          <t>-71,98; -5,93</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-12,29%</t>
+          <t>-9,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 6,08</t>
+          <t>-6,19; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,39</t>
+          <t>-3,15; 8,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,98</t>
+          <t>-1,51; 4,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,81</t>
+          <t>-7,16; 4,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 72,97</t>
+          <t>-47,23; 77,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 144,14</t>
+          <t>-27,11; 129,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 283,43</t>
+          <t>-43,83; 306,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 63,28</t>
+          <t>-51,32; 59,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-21,95%</t>
+          <t>-26,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -0,99</t>
+          <t>-8,24; -0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 0,26</t>
+          <t>-11,36; -0,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,03</t>
+          <t>-5,07; 3,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 4,21</t>
+          <t>-12,77; 1,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -10,8</t>
+          <t>-76,44; 1,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,08; 3,65</t>
+          <t>-67,29; -1,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 99,55</t>
+          <t>-56,31; 82,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 44,54</t>
+          <t>-65,36; 17,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>-26,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,43</t>
+          <t>-5,95; -0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,76</t>
+          <t>-5,1; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,06</t>
+          <t>-2,54; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 0,14</t>
+          <t>-7,49; -0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,94; -3,92</t>
+          <t>-45,33; -6,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 6,13</t>
+          <t>-32,06; 7,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 34,95</t>
+          <t>-31,63; 33,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 1,33</t>
+          <t>-47,18; -3,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP08-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-26,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-15,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-27,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-19,63%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.3704062078981</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.696314145818821</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.792004265723099</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.651102398339759</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2634307730218316</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1578383090547126</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2744532979222123</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1962693715775001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,7; 2,81</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 4,96</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,51; 2,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,1; 7,24</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-62,58; 33,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-45,4; 39,8</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-66,3; 37,47</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-61,42; 55,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.698468476475767</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.286753935840022</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-8.508114298318741</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.10461192115176</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6258263459197458</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4539879279153148</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6629909919353483</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6141870627700432</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.806412443560679</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.958989297943947</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.58577734300551</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.244447338260162</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3392816536929089</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3980393832979723</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3746515866527505</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.5519038686925695</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-4,11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,89</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-29,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-16,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-49,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,48; 0,55</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 2,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 4,66</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,59; -0,75</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,82; 6,13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-42,72; 19,19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-37,53; 72,7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,98; -5,93</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-4.10719110088854</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.309866300904928</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5708348983532396</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-5.891257870647839</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2965857329997556</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1617153453141214</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.0690866655091001</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4909365614498217</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,26%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.480407485320251</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.171228682930479</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.77305079824807</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.58605295197566</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5282351007041544</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4271869928021138</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3753227969695494</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7198111212979997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 5,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 8,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 4,87</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 4,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-47,23; 77,63</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-27,11; 129,75</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-43,83; 306,26</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-51,32; 59,35</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5517368301037212</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.450652897418576</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.661448046242896</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.7503386325760654</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06133287108657996</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1918700471398152</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7269854364211039</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.05929517609042442</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-4,57</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,54</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-52,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-41,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-9,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-26,37%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.06177214076519832</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.427418057156516</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.567570150556728</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.9971808459852849</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.00578454490850773</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3632783468923581</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4983716837464824</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09259954228712508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; -0,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,36; -0,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 3,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-12,77; 1,62</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-76,44; 1,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-67,29; -1,98</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-56,31; 82,45</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,36; 17,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.189650047150268</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.146945892342043</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.506355890133398</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.160987969559199</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4723090924229101</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2710673240429995</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4382797014931843</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5131569569072433</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.834185825798179</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.955014113558372</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.865018560000027</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.748372848384601</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.776291468272316</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.297450166309729</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.062611076553983</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5934585319831457</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-4.567396971946526</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-5.585227464642484</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6767325931495156</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.542738254159687</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5296219948522211</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4170820259294076</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.09968381250115994</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2637266856537528</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-8.244275614156207</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.35874079208624</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.065321705583686</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-12.76732019929656</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7644128338626703</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6729383748978011</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5630640521809137</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6535935131109943</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.3107019327064441</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.5104249070779909</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.802830691242085</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.621942061838545</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01597177749788512</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.01981988214607071</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8244551897028679</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1763079808748338</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-28,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-14,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-26,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,95; -0,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 0,8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 1,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,49; -0,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-45,33; -6,67</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-32,06; 7,29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,63; 33,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-47,18; -3,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-3.303284523888862</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.93139494561889</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.1506005161089757</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.319506118725754</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2857033034022324</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1420942007687196</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02171392135158616</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2609506388123771</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.954563579236132</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.095376117697031</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.540201451966159</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.492676257237084</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4532507148042993</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3205734876191109</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3163209210827836</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4718355910527177</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.7259770895151286</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8021662693662933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.946767346675045</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.4480021886639322</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.06674571181138882</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.07287206935443569</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3325198694159462</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.03114226194607941</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
